--- a/data/trans_camb/IP16A08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 15,23</t>
+          <t>-15,64; 15,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 28,45</t>
+          <t>-11,52; 28,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 8,27</t>
+          <t>-24,21; 7,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 20,58</t>
+          <t>-24,92; 20,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 17,5</t>
+          <t>-24,9; 18,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 6,35</t>
+          <t>-28,73; 8,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 15,45</t>
+          <t>-12,01; 15,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 16,15</t>
+          <t>-12,41; 17,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 4,73</t>
+          <t>-19,54; 4,53</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,19; —</t>
+          <t>-78,45; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,65; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 17,54</t>
+          <t>-23,89; 18,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 16,04</t>
+          <t>-23,85; 14,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 2,29</t>
+          <t>-36,47; 1,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 13,05</t>
+          <t>-22,71; 10,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 24,49</t>
+          <t>-14,13; 25,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 10,42</t>
+          <t>-23,35; 8,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 10,94</t>
+          <t>-16,22; 9,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 14,24</t>
+          <t>-13,51; 14,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 1,97</t>
+          <t>-22,23; 1,3</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,89; 183,8</t>
+          <t>-72,29; 245,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 147,41</t>
+          <t>-73,47; 156,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-94,37; 19,53</t>
+          <t>-93,2; 5,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,4; 227,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,35; 592,71</t>
+          <t>-69,11; 566,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,81; 282,84</t>
+          <t>-87,59; 223,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,71; 116,14</t>
+          <t>-65,17; 99,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 153,86</t>
+          <t>-55,0; 139,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 16,51</t>
+          <t>-81,72; 13,73</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 4,55</t>
+          <t>-34,77; 4,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 16,15</t>
+          <t>-25,79; 21,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 0,0</t>
+          <t>-38,6; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 7,19</t>
+          <t>-34,99; 8,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 27,24</t>
+          <t>-26,95; 29,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 11,96</t>
+          <t>-32,05; 11,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 3,28</t>
+          <t>-25,76; 3,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 15,38</t>
+          <t>-19,7; 15,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 2,25</t>
+          <t>-24,27; 2,91</t>
         </is>
       </c>
     </row>
@@ -1240,17 +1240,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 332,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 116,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 317,88</t>
+          <t>-100,0; 313,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 10,81</t>
+          <t>-27,52; 9,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 14,49</t>
+          <t>-22,43; 16,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 14,24</t>
+          <t>-25,96; 14,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 6,15</t>
+          <t>-33,21; 8,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-38,07; -0,61</t>
+          <t>-38,28; -0,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,27; -8,89</t>
+          <t>-46,32; -8,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 3,88</t>
+          <t>-23,5; 4,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 2,72</t>
+          <t>-26,88; 2,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-30,19; -3,06</t>
+          <t>-29,88; -1,63</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-87,78; —</t>
+          <t>-91,87; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,65</t>
+          <t>-91,95; 191,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-86,64; 55,92</t>
+          <t>-88,52; 57,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-86,43; 56,51</t>
+          <t>-88,0; 51,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,13</t>
+          <t>-100,0; 56,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-52,39; 9,94</t>
+          <t>-55,59; 7,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-65,84; -10,57</t>
+          <t>-62,91; -8,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-65,84; -10,51</t>
+          <t>-64,54; -8,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 0,0</t>
+          <t>-60,32; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 31,48</t>
+          <t>-37,38; 36,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 37,98</t>
+          <t>-34,73; 35,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-44,49; -4,42</t>
+          <t>-44,46; -3,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 2,73</t>
+          <t>-43,31; 2,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 9,08</t>
+          <t>-38,72; 11,5</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,24 +1677,24 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,94</t>
+          <t>-100,0; 5,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,51</t>
+          <t>-100,0; 254,15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 13,64</t>
+          <t>-40,9; 13,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-37,38; 26,94</t>
+          <t>-33,99; 28,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 5,15</t>
+          <t>-45,96; 6,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 5,74</t>
+          <t>-49,97; 3,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-46,28; 28,01</t>
+          <t>-47,43; 27,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-60,68; -11,01</t>
+          <t>-62,04; -12,82</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 2,98</t>
+          <t>-35,26; 1,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 15,68</t>
+          <t>-31,7; 15,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-44,35; -9,29</t>
+          <t>-44,16; -10,46</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 260,76</t>
+          <t>-100,0; 236,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 268,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-85,97; 31,6</t>
+          <t>-87,89; 24,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 168,34</t>
+          <t>-100,0; 127,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,25</t>
+          <t>-100,0; -18,37</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-78,55; 23,7</t>
+          <t>-78,64; 13,67</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 74,63</t>
+          <t>-75,5; 75,1</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-95,24; -15,84</t>
+          <t>-95,78; -34,87</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 22,17</t>
+          <t>-7,36; 22,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 34,53</t>
+          <t>-4,6; 34,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,13; 31,13</t>
+          <t>-1,35; 31,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 15,25</t>
+          <t>-13,27; 16,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 17,6</t>
+          <t>-15,95; 15,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 10,92</t>
+          <t>-14,91; 11,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 14,39</t>
+          <t>-6,59; 13,95</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 19,22</t>
+          <t>-6,68; 19,86</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 15,86</t>
+          <t>-5,05; 14,66</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-73,03; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,01; —</t>
+          <t>-40,41; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 606,55</t>
+          <t>-82,06; 469,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-88,88; 479,87</t>
+          <t>-88,03; 403,55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 390,43</t>
+          <t>-53,02; 387,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,78; 442,33</t>
+          <t>-67,94; 422,69</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 427,64</t>
+          <t>-41,62; 367,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 16,36</t>
+          <t>-12,62; 16,68</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 10,45</t>
+          <t>-16,05; 10,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 21,62</t>
+          <t>-15,95; 20,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 30,29</t>
+          <t>-2,73; 32,4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 26,54</t>
+          <t>-3,3; 26,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 42,76</t>
+          <t>-3,25; 45,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 19,19</t>
+          <t>-3,09; 19,35</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 15,72</t>
+          <t>-5,21; 15,83</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 29,83</t>
+          <t>-5,12; 30,72</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-83,84; 490,89</t>
+          <t>-84,8; 405,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 449,1</t>
+          <t>-26,74; 504,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 466,44</t>
+          <t>-30,92; 414,42</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 790,82</t>
+          <t>-41,97; 615,7</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 245,1</t>
+          <t>-28,08; 287,46</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 221,53</t>
+          <t>-42,46; 205,84</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 401,39</t>
+          <t>-46,31; 353,43</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 3,17</t>
+          <t>-9,8; 4,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 6,01</t>
+          <t>-9,26; 5,87</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -0,96</t>
+          <t>-13,71; -0,03</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 3,19</t>
+          <t>-10,07; 3,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 5,9</t>
+          <t>-9,1; 5,71</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 0,49</t>
+          <t>-12,45; 0,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,6</t>
+          <t>-8,1; 1,63</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,6</t>
+          <t>-6,57; 3,9</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -1,79</t>
+          <t>-11,23; -1,8</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 27,69</t>
+          <t>-51,46; 40,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 50,37</t>
+          <t>-47,77; 52,28</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-75,9; -7,28</t>
+          <t>-74,15; 0,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 29,04</t>
+          <t>-52,22; 26,0</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 46,29</t>
+          <t>-45,97; 46,43</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 3,61</t>
+          <t>-63,05; 4,68</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 14,17</t>
+          <t>-44,43; 12,35</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 35,96</t>
+          <t>-35,86; 30,23</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-61,31; -12,29</t>
+          <t>-61,91; -12,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 15,0</t>
+          <t>-18,29; 14,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 28,77</t>
+          <t>-8,75; 29,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 7,2</t>
+          <t>-22,88; 6,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 20,89</t>
+          <t>-23,93; 19,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 18,93</t>
+          <t>-25,89; 16,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 8,62</t>
+          <t>-30,14; 8,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 15,05</t>
+          <t>-13,71; 14,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 17,81</t>
+          <t>-11,12; 17,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 4,53</t>
+          <t>-18,68; 4,45</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,45; —</t>
+          <t>-82,3; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,65; —</t>
+          <t>-77,11; 573,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 18,85</t>
+          <t>-26,38; 16,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 14,89</t>
+          <t>-26,89; 14,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 1,71</t>
+          <t>-37,19; 1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 10,79</t>
+          <t>-20,75; 12,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 25,65</t>
+          <t>-14,16; 24,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 8,73</t>
+          <t>-21,12; 9,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 9,73</t>
+          <t>-17,44; 8,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 14,2</t>
+          <t>-13,8; 15,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 1,3</t>
+          <t>-24,19; 0,87</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,29; 245,32</t>
+          <t>-73,95; 163,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,47; 156,79</t>
+          <t>-73,86; 167,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-93,2; 5,5</t>
+          <t>-95,95; 20,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,4; 227,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,11; 566,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,59; 223,8</t>
+          <t>-82,28; 227,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,17; 99,39</t>
+          <t>-67,61; 88,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 139,21</t>
+          <t>-55,34; 148,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 13,73</t>
+          <t>-83,36; 3,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 4,52</t>
+          <t>-28,7; 6,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 21,98</t>
+          <t>-26,01; 15,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 0,0</t>
+          <t>-38,52; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 8,57</t>
+          <t>-34,93; 8,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 29,73</t>
+          <t>-25,87; 29,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 11,17</t>
+          <t>-30,74; 13,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 3,55</t>
+          <t>-24,43; 3,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 15,13</t>
+          <t>-19,17; 16,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 2,91</t>
+          <t>-24,57; 3,33</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 332,22</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 313,07</t>
+          <t>-100,0; 293,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 142,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 9,36</t>
+          <t>-29,57; 7,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 16,66</t>
+          <t>-26,14; 13,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 14,91</t>
+          <t>-26,19; 15,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 8,97</t>
+          <t>-34,73; 8,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-38,28; -0,28</t>
+          <t>-37,41; -0,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,32; -8,61</t>
+          <t>-48,2; -8,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 4,25</t>
+          <t>-25,07; 3,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 2,51</t>
+          <t>-25,34; 2,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-29,88; -1,63</t>
+          <t>-29,34; -1,73</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,87; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-91,95; 191,68</t>
+          <t>-90,83; 136,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 66,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-88,52; 57,5</t>
+          <t>-87,23; 74,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,0; 51,31</t>
+          <t>-85,98; 49,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,4</t>
+          <t>-100,0; 53,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 7,54</t>
+          <t>-54,83; 4,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-62,91; -8,42</t>
+          <t>-65,84; -10,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-64,54; -8,42</t>
+          <t>-65,7; -10,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 0,0</t>
+          <t>-52,87; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,38; 36,83</t>
+          <t>-35,1; 33,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 35,44</t>
+          <t>-34,93; 33,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -3,24</t>
+          <t>-46,45; -4,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-43,31; 2,71</t>
+          <t>-45,57; 1,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 11,5</t>
+          <t>-40,19; 7,66</t>
         </is>
       </c>
     </row>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 5,41</t>
+          <t>-100,0; 12,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 123,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 254,15</t>
+          <t>-100,0; 191,48</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 13,94</t>
+          <t>-41,4; 11,73</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 28,14</t>
+          <t>-35,7; 24,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 6,8</t>
+          <t>-48,03; 3,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-49,97; 3,23</t>
+          <t>-49,11; 4,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 27,4</t>
+          <t>-46,69; 22,57</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-62,04; -12,82</t>
+          <t>-59,69; -9,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 1,91</t>
+          <t>-37,96; 2,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 15,69</t>
+          <t>-32,17; 17,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-44,16; -10,46</t>
+          <t>-45,17; -11,61</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,83; 174,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 236,0</t>
+          <t>-85,22; 181,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-87,89; 24,12</t>
+          <t>-86,72; 28,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,9</t>
+          <t>-87,29; 97,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -18,37</t>
+          <t>-100,0; -4,53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-78,64; 13,67</t>
+          <t>-79,6; 14,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-75,5; 75,1</t>
+          <t>-74,45; 81,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-95,78; -34,87</t>
+          <t>-94,92; -26,06</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 22,87</t>
+          <t>-7,46; 21,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 34,37</t>
+          <t>-4,29; 34,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 31,53</t>
+          <t>-2,02; 29,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 16,15</t>
+          <t>-12,11; 16,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 15,64</t>
+          <t>-15,62; 14,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 11,67</t>
+          <t>-14,65; 12,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 13,95</t>
+          <t>-6,1; 15,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 19,86</t>
+          <t>-7,31; 19,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 14,66</t>
+          <t>-5,95; 15,31</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,11; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,41; —</t>
+          <t>-48,96; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-82,06; 469,19</t>
+          <t>-80,99; 653,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-88,03; 403,55</t>
+          <t>-84,9; 488,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 387,01</t>
+          <t>-53,45; 374,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-67,94; 422,69</t>
+          <t>-65,86; 475,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 367,65</t>
+          <t>-47,54; 371,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 16,68</t>
+          <t>-12,08; 16,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 10,14</t>
+          <t>-15,71; 11,34</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 20,31</t>
+          <t>-16,12; 19,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 32,4</t>
+          <t>-2,17; 32,72</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 26,33</t>
+          <t>-2,93; 26,06</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 45,0</t>
+          <t>-3,99; 43,24</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 19,35</t>
+          <t>-4,54; 19,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 15,83</t>
+          <t>-7,16; 15,6</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 30,72</t>
+          <t>-4,8; 28,14</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-84,8; 405,89</t>
+          <t>-84,88; 428,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 504,31</t>
+          <t>-26,79; 619,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 414,42</t>
+          <t>-26,74; 467,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 615,7</t>
+          <t>-41,6; 574,37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 287,46</t>
+          <t>-34,97; 280,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,46; 205,84</t>
+          <t>-48,71; 223,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,31; 353,43</t>
+          <t>-45,99; 405,43</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 4,34</t>
+          <t>-10,43; 2,88</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 5,87</t>
+          <t>-8,83; 6,24</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,03</t>
+          <t>-14,55; -0,56</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 3,36</t>
+          <t>-10,08; 2,99</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 5,71</t>
+          <t>-9,09; 6,11</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 0,44</t>
+          <t>-12,48; 0,74</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 1,63</t>
+          <t>-8,57; 1,38</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 3,9</t>
+          <t>-6,41; 4,03</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -1,8</t>
+          <t>-11,46; -2,28</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 40,41</t>
+          <t>-54,05; 27,86</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 52,28</t>
+          <t>-47,38; 55,38</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 0,03</t>
+          <t>-74,8; -6,13</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-52,22; 26,0</t>
+          <t>-50,24; 25,11</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 46,43</t>
+          <t>-45,31; 51,59</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 4,68</t>
+          <t>-61,83; 7,15</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 12,35</t>
+          <t>-45,18; 10,24</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 30,23</t>
+          <t>-34,73; 31,52</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-61,91; -12,72</t>
+          <t>-61,37; -15,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A08-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,02</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,94</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,56</t>
+          <t>-3,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 14,32</t>
+          <t>-23,59; 20,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 29,68</t>
+          <t>-24,3; 17,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 6,92</t>
+          <t>-30,47; 7,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 19,68</t>
+          <t>-18,15; 15,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 16,73</t>
+          <t>-11,09; 28,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,14; 8,45</t>
+          <t>-19,27; 11,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 14,05</t>
+          <t>-12,31; 15,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 17,49</t>
+          <t>-11,71; 16,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 4,45</t>
+          <t>-18,07; 6,49</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-10,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-48,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>19,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>142,94%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-33,49%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-10,62%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-52,78%</t>
+          <t>-9,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-48,14%</t>
+          <t>-35,65%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,3; —</t>
+          <t>-82,19; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 573,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,78</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,87</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-14,36</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,43</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-8,7</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,95</t>
+          <t>-5,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 16,11</t>
+          <t>-21,0; 13,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 14,92</t>
+          <t>-13,48; 24,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 1,95</t>
+          <t>-20,08; 11,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 12,26</t>
+          <t>-25,97; 17,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 24,63</t>
+          <t>-24,6; 16,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 9,31</t>
+          <t>-30,92; 7,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 8,68</t>
+          <t>-17,03; 10,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 15,19</t>
+          <t>-12,31; 14,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 0,87</t>
+          <t>-19,33; 5,65</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-24,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-26,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-13,13%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-17,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-63,65%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-24,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-28,39%</t>
+          <t>-38,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-49,78%</t>
+          <t>-33,17%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,95; 163,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 167,09</t>
+          <t>-74,35; 592,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-95,95; 20,85</t>
+          <t>-80,03; 302,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,89; 183,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,36; 147,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,28; 227,24</t>
+          <t>-80,99; 96,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,61; 88,07</t>
+          <t>-65,71; 116,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,34; 148,76</t>
+          <t>-50,77; 153,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,36; 3,15</t>
+          <t>-72,52; 61,37</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-10,29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,68</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,48</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-8,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,46</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-12,74</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-10,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-7,01</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-8,94</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-9,43</t>
+          <t>-9,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 6,43</t>
+          <t>-35,67; 7,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 15,51</t>
+          <t>-28,59; 27,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 0,0</t>
+          <t>-31,68; 12,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 8,52</t>
+          <t>-35,08; 4,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 29,29</t>
+          <t>-25,26; 16,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 13,52</t>
+          <t>-37,85; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 3,39</t>
+          <t>-25,02; 3,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 16,03</t>
+          <t>-19,76; 15,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 3,33</t>
+          <t>-26,19; 2,3</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-58,12%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-3,87%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-36,6%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-65,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-42,82%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-58,12%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-39,6%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-59,19%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-62,43%</t>
+          <t>-62,33%</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 293,97</t>
+          <t>-100,0; 317,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 142,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-11,21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-17,3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-22,65</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-7,17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,52</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-11,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-17,3</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-22,65</t>
+          <t>-6,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,93</t>
+          <t>-14,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 7,99</t>
+          <t>-34,31; 6,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 13,77</t>
+          <t>-38,07; -0,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 15,99</t>
+          <t>-44,27; -8,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 8,0</t>
+          <t>-25,31; 10,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -0,25</t>
+          <t>-24,91; 14,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,2; -8,72</t>
+          <t>-26,08; 16,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 3,41</t>
+          <t>-23,77; 3,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 2,64</t>
+          <t>-25,28; 2,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-29,34; -1,73</t>
+          <t>-29,94; -1,38</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-49,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-76,35%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-47,46%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-16,69%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-50,68%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-49,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-76,35%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-44,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-79,07%</t>
+          <t>-76,04%</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 90,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-90,83; 136,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,5</t>
+          <t>-87,78; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,23; 74,95</t>
+          <t>-86,64; 55,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-85,98; 49,81</t>
+          <t>-86,43; 56,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 53,77</t>
+          <t>-100,0; 51,38</t>
         </is>
       </c>
     </row>
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-21,5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-6,15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-8,7</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-22,85</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-35,19</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-35,19</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-21,5</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-6,15</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>-22,19</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-17,27</t>
+          <t>-22,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 4,87</t>
+          <t>-53,16; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-65,84; -10,49</t>
+          <t>-41,71; 31,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-65,7; -10,48</t>
+          <t>-48,92; 18,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 0,0</t>
+          <t>-52,39; 9,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 33,37</t>
+          <t>-65,84; -10,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 33,83</t>
+          <t>-65,84; -10,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-46,45; -4,52</t>
+          <t>-44,49; -4,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 1,72</t>
+          <t>-43,18; 2,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 7,66</t>
+          <t>-43,26; -0,84</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-28,62%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-40,48%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-64,92%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-28,62%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-4,45%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>-76,85%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-59,82%</t>
+          <t>-76,26%</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,18</t>
+          <t>-100,0; 26,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,89</t>
+          <t>-100,0; 121,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 191,48</t>
+          <t>-100,0; 29,87</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-22,62</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-12,82</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-34,16</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-13,45</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-5,78</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-21,38</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-22,62</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-12,82</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-34,69</t>
+          <t>-21,06</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-27,66</t>
+          <t>-27,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-41,4; 11,73</t>
+          <t>-50,74; 5,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 24,22</t>
+          <t>-46,28; 28,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 3,71</t>
+          <t>-59,58; -9,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 4,87</t>
+          <t>-41,07; 13,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 22,57</t>
+          <t>-37,38; 26,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-59,69; -9,86</t>
+          <t>-44,77; 6,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 2,17</t>
+          <t>-35,01; 2,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 17,08</t>
+          <t>-32,12; 15,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-45,17; -11,61</t>
+          <t>-44,19; -8,04</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-54,59%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-30,92%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-82,43%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-46,86%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-20,14%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-74,49%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-54,59%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-30,92%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-83,71%</t>
+          <t>-73,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-79,9%</t>
+          <t>-78,55%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-90,83; 174,35</t>
+          <t>-85,97; 31,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-85,22; 181,9</t>
+          <t>-83,28; 168,34</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -14,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 28,86</t>
+          <t>-100,0; 146,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-87,29; 97,29</t>
+          <t>-100,0; 260,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,53</t>
+          <t>-100,0; 286,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 14,18</t>
+          <t>-78,55; 23,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,45; 81,53</t>
+          <t>-71,39; 74,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-94,92; -26,06</t>
+          <t>-96,35; -10,71</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-4,2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,88</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>7,42</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>12,88</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>14,95</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-4,2</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>15,75</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>6,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 21,36</t>
+          <t>-11,74; 15,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 34,07</t>
+          <t>-15,77; 17,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 29,51</t>
+          <t>-13,86; 12,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 16,54</t>
+          <t>-4,86; 22,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 14,89</t>
+          <t>-4,57; 34,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 12,17</t>
+          <t>1,92; 32,53</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 15,19</t>
+          <t>-6,13; 14,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 19,38</t>
+          <t>-6,42; 19,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 15,31</t>
+          <t>-3,91; 17,67</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-40,6%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-8,46%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>110,46%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>191,79%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>222,57%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-40,6%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-15,23%</t>
+          <t>234,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-74,11; —</t>
+          <t>-81,19; 606,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-48,96; —</t>
+          <t>-89,52; 484,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-80,99; 653,22</t>
+          <t>-73,03; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-84,9; 488,74</t>
+          <t>-15,81; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 374,72</t>
+          <t>-51,61; 390,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 475,63</t>
+          <t>-63,78; 442,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 371,42</t>
+          <t>-40,56; 459,92</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>12,25</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10,6</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>17,16</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>1,65</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-3,18</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>12,25</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>10,6</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,08</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>8,98</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 16,39</t>
+          <t>-4,84; 30,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 11,34</t>
+          <t>-4,62; 26,54</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 19,19</t>
+          <t>-3,99; 44,57</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 32,72</t>
+          <t>-12,66; 16,36</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 26,06</t>
+          <t>-16,22; 10,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 43,24</t>
+          <t>-15,82; 19,88</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 19,11</t>
+          <t>-4,01; 19,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 15,6</t>
+          <t>-5,35; 15,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 28,14</t>
+          <t>-5,73; 31,42</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>105,73%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>148,12%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-30,5%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-28,69%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>105,73%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>91,47%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>138,84%</t>
+          <t>-34,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-84,88; 428,85</t>
+          <t>-38,57; 449,1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-36,14; 466,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-45,82; 817,39</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 619,48</t>
+          <t>-83,84; 490,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 467,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 574,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 280,2</t>
+          <t>-34,41; 245,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 223,36</t>
+          <t>-40,9; 221,53</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,99; 405,43</t>
+          <t>-52,33; 430,07</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-3,58</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-5,91</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-3,39</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-1,63</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-7,02</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-4,62</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-6,55</t>
+          <t>-5,31</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 2,88</t>
+          <t>-9,92; 3,19</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 6,24</t>
+          <t>-8,46; 5,9</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -0,56</t>
+          <t>-12,79; 0,68</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 2,99</t>
+          <t>-10,6; 3,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 6,11</t>
+          <t>-9,21; 6,01</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 0,74</t>
+          <t>-11,67; 2,54</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,38</t>
+          <t>-8,18; 1,6</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 4,03</t>
+          <t>-6,51; 4,6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -2,28</t>
+          <t>-10,28; -0,3</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-21,99%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-8,87%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-36,33%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-21,95%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-10,54%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-45,44%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-21,99%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-8,87%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-37,21%</t>
+          <t>-29,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-41,25%</t>
+          <t>-33,42%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 27,86</t>
+          <t>-50,5; 29,04</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 55,38</t>
+          <t>-41,9; 46,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-74,8; -6,13</t>
+          <t>-63,63; 6,75</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 25,11</t>
+          <t>-52,17; 27,69</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 51,59</t>
+          <t>-48,12; 50,37</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 7,15</t>
+          <t>-62,25; 21,35</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 10,24</t>
+          <t>-44,94; 14,17</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 31,52</t>
+          <t>-35,98; 35,96</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-61,37; -15,04</t>
+          <t>-55,93; -2,26</t>
         </is>
       </c>
     </row>
